--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>256879</v>
+        <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>83204</v>
+        <v>92906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>779</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tesås, Sm</t>
+          <t>Sälleberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453484</v>
+        <v>453355</v>
       </c>
       <c r="R2" t="n">
-        <v>6301614</v>
+        <v>6301516</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-09-20</t>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>med klubbor</t>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,41 +782,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>lindlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Anders Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Anders Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/256879</t>
+          <t>https://artportalen.se/Sighting/136708381</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>522867</v>
+        <v>256879</v>
       </c>
       <c r="B3" t="n">
-        <v>97785</v>
+        <v>83204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +841,16 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tesås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453552</v>
+        <v>453484</v>
       </c>
       <c r="R3" t="n">
-        <v>6301476</v>
+        <v>6301614</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,6 +885,11 @@
           <t>2008-09-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>med klubbor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +906,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på klippa</t>
+          <t>lindlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,13 +923,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/522867</t>
+          <t>https://artportalen.se/Sighting/256879</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>522868</v>
+        <v>522867</v>
       </c>
       <c r="B4" t="n">
         <v>97785</v>
@@ -962,7 +959,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453521</v>
+        <v>453552</v>
       </c>
       <c r="R4" t="n">
-        <v>6301557</v>
+        <v>6301476</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1033,6 +1030,11 @@
           <t>Lövskog</t>
         </is>
       </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på klippa</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1047,13 +1049,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/522868</t>
+          <t>https://artportalen.se/Sighting/522867</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91557262</v>
+        <v>522868</v>
       </c>
       <c r="B5" t="n">
         <v>97785</v>
@@ -1083,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1093,21 +1095,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norragården, Tesås, Sm</t>
+          <t>Tesås, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453379</v>
+        <v>453521</v>
       </c>
       <c r="R5" t="n">
-        <v>6301660</v>
+        <v>6301557</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,17 +1134,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2008-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en levande asp</t>
+          <t>2008-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,9 +1148,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1171,16 +1170,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91557262</t>
+          <t>https://artportalen.se/Sighting/522868</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>743379</v>
+        <v>91557262</v>
       </c>
       <c r="B6" t="n">
-        <v>96426</v>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,26 +1187,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1217,19 +1216,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tesås, Sm</t>
+          <t>Norragården, Tesås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453554</v>
+        <v>453379</v>
       </c>
       <c r="R6" t="n">
-        <v>6301483</v>
+        <v>6301660</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1256,12 +1257,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2008-09-20</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2008-09-20</t>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en levande asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,18 +1276,9 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>sten</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1297,13 +1294,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/743379</t>
+          <t>https://artportalen.se/Sighting/91557262</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>743380</v>
+        <v>743379</v>
       </c>
       <c r="B7" t="n">
         <v>96426</v>
@@ -1333,7 +1330,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453494</v>
+        <v>453554</v>
       </c>
       <c r="R7" t="n">
-        <v>6301613</v>
+        <v>6301483</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1406,7 +1403,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>lind</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1423,16 +1420,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/743380</t>
+          <t>https://artportalen.se/Sighting/743379</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>742862</v>
+        <v>743380</v>
       </c>
       <c r="B8" t="n">
-        <v>96231</v>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,26 +1437,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1549,16 +1546,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/742862</t>
+          <t>https://artportalen.se/Sighting/743380</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5042052</v>
+        <v>742862</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>96231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,24 +1563,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1595,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453556</v>
+        <v>453494</v>
       </c>
       <c r="R9" t="n">
-        <v>6301477</v>
+        <v>6301613</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1633,11 +1639,6 @@
           <t>2008-09-20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1650,6 +1651,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>lind</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,13 +1672,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5042052</t>
+          <t>https://artportalen.se/Sighting/742862</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5042053</v>
+        <v>5042052</v>
       </c>
       <c r="B10" t="n">
         <v>101326</v>
@@ -1700,16 +1706,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1721,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453516</v>
+        <v>453556</v>
       </c>
       <c r="R10" t="n">
-        <v>6301565</v>
+        <v>6301477</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1761,7 +1758,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>grönsten</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,13 +1789,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5042053</t>
+          <t>https://artportalen.se/Sighting/5042052</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5042054</v>
+        <v>5042053</v>
       </c>
       <c r="B11" t="n">
         <v>101326</v>
@@ -1828,7 +1825,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1847,10 +1844,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453580</v>
+        <v>453516</v>
       </c>
       <c r="R11" t="n">
-        <v>6301475</v>
+        <v>6301565</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1885,6 +1882,11 @@
           <t>2008-09-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>grönsten</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1912,6 +1914,127 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5042053</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5042054</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tesås, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>453580</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6301475</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2008-09-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2008-09-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5042054</t>
         </is>
@@ -1929,6 +2052,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1913-2025 artfynd.xlsx
+++ b/artfynd/S 1913-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708381</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
